--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2689F36F-DC65-43A3-8DB2-91A7BAE05493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092CF145-145C-4CA6-9434-3B4D98BBCF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5065,7 +5065,7 @@
         <v>46176.432986111111</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K161" t="s">
         <v>11</v>
@@ -5094,7 +5094,7 @@
         <v>46176.433680555558</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162" t="s">
         <v>11</v>
@@ -5123,7 +5123,7 @@
         <v>46176.433680555558</v>
       </c>
       <c r="J163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K163" t="s">
         <v>11</v>
@@ -5152,7 +5152,7 @@
         <v>46176.419212962966</v>
       </c>
       <c r="J164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K164" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66F467FA-CE7B-41B0-A00C-842380F4E7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D444AD24-04C0-49D3-952C-A61D829D6B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="51">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,9 +86,6 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
-  </si>
-  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -98,13 +95,16 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Alert Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -116,40 +116,31 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
     <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
-    <t>DNU-Driver Health</t>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>DNU-Fatigue</t>
+    <t>3 points of contact</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
-    <t>Micro-Learn Safe Following Distance</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>STAC Services</t>
@@ -188,10 +179,19 @@
     <t>DNU-UpdatedNEWMicro-LearnSpeed</t>
   </si>
   <si>
+    <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Micro-Learn Safe Following Distance</t>
+  </si>
+  <si>
     <t>Alejandro Garza</t>
   </si>
   <si>
     <t>Michael Vesely</t>
+  </si>
+  <si>
+    <t>Speed Management</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -614,16 +614,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>1227</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -643,16 +643,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>1229</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -672,16 +672,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>1228</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -701,16 +701,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>1230</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -730,16 +730,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>1232</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -759,16 +759,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>1231</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -788,16 +788,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>1233</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -817,16 +817,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>1234</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -846,16 +846,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>1227</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -875,16 +875,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>1229</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -904,16 +904,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>1228</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>14</v>
@@ -937,21 +937,21 @@
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>1230</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>12</v>
@@ -975,21 +975,21 @@
       <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>1232</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1009,16 +1009,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E17">
         <v>1231</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1038,16 +1038,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>1233</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>12</v>
@@ -1071,21 +1071,21 @@
       <c r="J19" s="2"/>
       <c r="K19" s="1"/>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20">
         <v>1234</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>1229</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>1228</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>14</v>
@@ -1167,21 +1167,21 @@
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <v>1230</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>14</v>
@@ -1205,21 +1205,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E26">
         <v>1232</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1239,16 +1239,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E27">
         <v>1231</v>
       </c>
       <c r="F27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1268,16 +1268,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E28">
         <v>1233</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1297,16 +1297,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E29">
         <v>1234</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E30">
         <v>1229</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E31">
         <v>1228</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E32">
         <v>1230</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1232</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1231</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1471,16 +1471,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>1233</v>
       </c>
       <c r="F35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1500,16 +1500,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E36">
         <v>1234</v>
       </c>
       <c r="F36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -1529,16 +1529,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E37">
         <v>1229</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1558,16 +1558,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E38">
         <v>1228</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1587,16 +1587,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>1230</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1616,16 +1616,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>1232</v>
       </c>
       <c r="F40" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1645,16 +1645,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E41">
         <v>1231</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E42">
         <v>1233</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1703,16 +1703,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E43">
         <v>1234</v>
       </c>
       <c r="F43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1732,16 +1732,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E44">
         <v>1229</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1761,16 +1761,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E45">
         <v>1228</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1790,16 +1790,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E46">
         <v>1230</v>
       </c>
       <c r="F46" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E47">
         <v>1232</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1848,16 +1848,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E48">
         <v>1231</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E49">
         <v>1233</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E50">
         <v>1234</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -1935,16 +1935,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E51">
         <v>1229</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -1964,16 +1964,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E52">
         <v>1228</v>
       </c>
       <c r="F52" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1993,16 +1993,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E53">
         <v>1230</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2022,16 +2022,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E54">
         <v>1232</v>
       </c>
       <c r="F54" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E55">
         <v>1231</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -2080,16 +2080,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E56">
         <v>1233</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2109,16 +2109,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E57">
         <v>1234</v>
       </c>
       <c r="F57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2138,16 +2138,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E58">
         <v>1229</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2167,16 +2167,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E59">
         <v>1228</v>
       </c>
       <c r="F59" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E60">
         <v>1230</v>
       </c>
       <c r="F60" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>12</v>
@@ -2229,21 +2229,21 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E62">
         <v>1232</v>
       </c>
       <c r="F62" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E63">
         <v>1231</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E64">
         <v>1233</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E65">
         <v>1234</v>
       </c>
       <c r="F65" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E66">
         <v>1229</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E67">
         <v>1228</v>
       </c>
       <c r="F67" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2408,16 +2408,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E68">
         <v>1230</v>
       </c>
       <c r="F68" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2437,16 +2437,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E69">
         <v>1232</v>
       </c>
       <c r="F69" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E70">
         <v>1231</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E71">
         <v>1233</v>
       </c>
       <c r="F71" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>13</v>
@@ -2524,16 +2524,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E72">
         <v>1234</v>
       </c>
       <c r="F72" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2553,16 +2553,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E73">
         <v>1229</v>
       </c>
       <c r="F73" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E74">
         <v>1228</v>
       </c>
       <c r="F74" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E75">
         <v>1230</v>
       </c>
       <c r="F75" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2644,21 +2644,21 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E77">
         <v>1232</v>
       </c>
       <c r="F77" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2678,16 +2678,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E78">
         <v>1231</v>
       </c>
       <c r="F78" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2707,16 +2707,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E79">
         <v>1233</v>
       </c>
       <c r="F79" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2736,16 +2736,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E80">
         <v>1234</v>
       </c>
       <c r="F80" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2765,16 +2765,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E81">
         <v>1229</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E82">
         <v>1228</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2823,16 +2823,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E83">
         <v>1230</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2852,16 +2852,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E84">
         <v>1232</v>
       </c>
       <c r="F84" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2881,16 +2881,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E85">
         <v>1231</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2910,16 +2910,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E86">
         <v>1234</v>
       </c>
       <c r="F86" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2939,16 +2939,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E87">
         <v>1229</v>
       </c>
       <c r="F87" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -2968,16 +2968,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E88">
         <v>1228</v>
       </c>
       <c r="F88" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -2997,16 +2997,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E89">
         <v>1230</v>
       </c>
       <c r="F89" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3026,16 +3026,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E90">
         <v>1232</v>
       </c>
       <c r="F90" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3055,16 +3055,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E91">
         <v>1231</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3084,16 +3084,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E92">
         <v>1234</v>
       </c>
       <c r="F92" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3113,16 +3113,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>1229</v>
       </c>
       <c r="F93" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3142,16 +3142,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E94">
         <v>1228</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3171,16 +3171,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E95">
         <v>1230</v>
       </c>
       <c r="F95" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>12</v>
@@ -3204,21 +3204,21 @@
       <c r="J96" s="2"/>
       <c r="K96" s="1"/>
       <c r="M96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E97">
         <v>1232</v>
       </c>
       <c r="F97" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3238,16 +3238,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E98">
         <v>1231</v>
       </c>
       <c r="F98" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3267,16 +3267,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E99">
         <v>1234</v>
       </c>
       <c r="F99" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3296,16 +3296,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E100">
         <v>1229</v>
       </c>
       <c r="F100" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3325,16 +3325,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E101">
         <v>1228</v>
       </c>
       <c r="F101" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>12</v>
@@ -3358,21 +3358,21 @@
       <c r="J102" s="2"/>
       <c r="K102" s="1"/>
       <c r="M102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E103">
         <v>1230</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E104">
         <v>1232</v>
       </c>
       <c r="F104" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3421,16 +3421,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E105">
         <v>1231</v>
       </c>
       <c r="F105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3450,16 +3450,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E106">
         <v>1234</v>
       </c>
       <c r="F106" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3479,16 +3479,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E107">
         <v>1229</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3508,16 +3508,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E108">
         <v>1228</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3537,16 +3537,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E109">
         <v>1230</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3566,16 +3566,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E110">
         <v>1232</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3595,16 +3595,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E111">
         <v>1231</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3624,16 +3624,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E112">
         <v>1234</v>
       </c>
       <c r="F112" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3653,16 +3653,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E113">
         <v>1229</v>
       </c>
       <c r="F113" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E114">
         <v>1228</v>
       </c>
       <c r="F114" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3711,16 +3711,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E115">
         <v>1230</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3740,16 +3740,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E116">
         <v>1232</v>
       </c>
       <c r="F116" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3769,16 +3769,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E117">
         <v>1231</v>
       </c>
       <c r="F117" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3798,16 +3798,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E118">
         <v>1234</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3827,16 +3827,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E119">
         <v>1229</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3856,16 +3856,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E120">
         <v>1228</v>
       </c>
       <c r="F120" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3885,16 +3885,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E121">
         <v>1230</v>
       </c>
       <c r="F121" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E122">
         <v>1232</v>
       </c>
       <c r="F122" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3943,16 +3943,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E123">
         <v>1231</v>
       </c>
       <c r="F123" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E124">
         <v>1234</v>
       </c>
       <c r="F124" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -4001,16 +4001,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E125">
         <v>1229</v>
       </c>
       <c r="F125" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4030,16 +4030,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E126">
         <v>1230</v>
       </c>
       <c r="F126" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E127">
         <v>1232</v>
       </c>
       <c r="F127" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4088,16 +4088,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E128">
         <v>1231</v>
       </c>
       <c r="F128" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4117,16 +4117,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E129">
         <v>1229</v>
       </c>
       <c r="F129" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4146,16 +4146,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E130">
         <v>1230</v>
       </c>
       <c r="F130" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4175,16 +4175,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E131">
         <v>1232</v>
       </c>
       <c r="F131" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4204,16 +4204,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E132">
         <v>1231</v>
       </c>
       <c r="F132" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4233,16 +4233,16 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E133">
         <v>1229</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4262,16 +4262,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E134">
         <v>1230</v>
       </c>
       <c r="F134" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4291,16 +4291,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E135">
         <v>1232</v>
       </c>
       <c r="F135" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4320,16 +4320,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E136">
         <v>1231</v>
       </c>
       <c r="F136" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4349,13 +4349,13 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E137">
         <v>5138</v>
       </c>
       <c r="F137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>22</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E138">
         <v>1229</v>
       </c>
       <c r="F138" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>22</v>
@@ -4407,13 +4407,13 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E139">
         <v>1230</v>
       </c>
       <c r="F139" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>22</v>
@@ -4436,13 +4436,13 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E140">
         <v>1232</v>
       </c>
       <c r="F140" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>22</v>
@@ -4465,13 +4465,13 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E141">
         <v>1231</v>
       </c>
       <c r="F141" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>22</v>
@@ -4494,16 +4494,16 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E142">
         <v>5138</v>
       </c>
       <c r="F142" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4523,16 +4523,16 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E143">
         <v>1229</v>
       </c>
       <c r="F143" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4552,16 +4552,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E144">
         <v>1230</v>
       </c>
       <c r="F144" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4581,16 +4581,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E145">
         <v>1232</v>
       </c>
       <c r="F145" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4610,16 +4610,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E146">
         <v>1231</v>
       </c>
       <c r="F146" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4639,16 +4639,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E147">
         <v>1229</v>
       </c>
       <c r="F147" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E148">
         <v>1230</v>
       </c>
       <c r="F148" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4697,16 +4697,16 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E149">
         <v>1232</v>
       </c>
       <c r="F149" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4726,16 +4726,16 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E150">
         <v>1231</v>
       </c>
       <c r="F150" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -4755,13 +4755,13 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E151">
         <v>1229</v>
       </c>
       <c r="F151" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>23</v>
@@ -4784,13 +4784,13 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E152">
         <v>1230</v>
       </c>
       <c r="F152" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>23</v>
@@ -4813,13 +4813,13 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E153">
         <v>1232</v>
       </c>
       <c r="F153" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>23</v>
@@ -4842,13 +4842,13 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E154">
         <v>1231</v>
       </c>
       <c r="F154" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>23</v>
@@ -4871,16 +4871,16 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E155">
         <v>1229</v>
       </c>
       <c r="F155" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4900,16 +4900,16 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E156">
         <v>1230</v>
       </c>
       <c r="F156" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4929,16 +4929,16 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E157">
         <v>5544</v>
       </c>
       <c r="F157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4958,16 +4958,16 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E158">
         <v>1232</v>
       </c>
       <c r="F158" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -4987,16 +4987,16 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E159">
         <v>1231</v>
       </c>
       <c r="F159" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5016,16 +5016,16 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E160">
         <v>5544</v>
       </c>
       <c r="F160" t="s">
+        <v>49</v>
+      </c>
+      <c r="H160" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="H160" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5045,13 +5045,13 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E161">
         <v>1229</v>
       </c>
       <c r="F161" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>24</v>
@@ -5074,13 +5074,13 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E162">
         <v>1230</v>
       </c>
       <c r="F162" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>24</v>
@@ -5103,13 +5103,13 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E163">
         <v>1232</v>
       </c>
       <c r="F163" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>24</v>
@@ -5132,13 +5132,13 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E164">
         <v>1231</v>
       </c>
       <c r="F164" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>24</v>
@@ -5160,34 +5160,149 @@
       </c>
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="2"/>
-      <c r="K165" s="1"/>
+      <c r="D165" t="s">
+        <v>34</v>
+      </c>
+      <c r="E165">
+        <v>1229</v>
+      </c>
+      <c r="F165" t="s">
+        <v>36</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J165" s="2">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1">
+        <v>46212.774652777778</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H166" s="2"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="2"/>
-      <c r="K166" s="1"/>
+      <c r="D166" t="s">
+        <v>34</v>
+      </c>
+      <c r="E166">
+        <v>1230</v>
+      </c>
+      <c r="F166" t="s">
+        <v>38</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="2">
+        <v>0</v>
+      </c>
+      <c r="K166" s="1">
+        <v>46212.775347222225</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H167" s="2"/>
-      <c r="I167" s="1"/>
-      <c r="J167" s="2"/>
-      <c r="K167" s="1"/>
+      <c r="D167" t="s">
+        <v>34</v>
+      </c>
+      <c r="E167">
+        <v>5544</v>
+      </c>
+      <c r="F167" t="s">
+        <v>49</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="2">
+        <v>0</v>
+      </c>
+      <c r="K167" s="1">
+        <v>46212.775347222225</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H168" s="2"/>
-      <c r="I168" s="1"/>
-      <c r="J168" s="2"/>
-      <c r="K168" s="1"/>
+      <c r="D168" t="s">
+        <v>34</v>
+      </c>
+      <c r="E168">
+        <v>1232</v>
+      </c>
+      <c r="F168" t="s">
+        <v>39</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J168" s="2">
+        <v>5.9375000000000001E-3</v>
+      </c>
+      <c r="K168" s="1">
+        <v>46212.776041666664</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H169" s="2"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="2"/>
-      <c r="K169" s="1"/>
+      <c r="D169" t="s">
+        <v>34</v>
+      </c>
+      <c r="E169">
+        <v>1231</v>
+      </c>
+      <c r="F169" t="s">
+        <v>40</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="2">
+        <v>0</v>
+      </c>
+      <c r="K169" s="1">
+        <v>46212.776736111111</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H170" s="2"/>
@@ -42652,7 +42767,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D444AD24-04C0-49D3-952C-A61D829D6B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{554F1467-B5A2-4F42-99E8-1D73CCE3CCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,6 +86,15 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -95,13 +104,16 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
+    <t>Alert Driving</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
@@ -110,28 +122,25 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
+  </si>
+  <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
-  </si>
-  <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
+  </si>
+  <si>
+    <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
     <t>Hazcom for CDL Drivers</t>
@@ -141,6 +150,9 @@
   </si>
   <si>
     <t>DNU-Fatigue</t>
+  </si>
+  <si>
+    <t>DNU-MicroLearn-In Cab Distractions</t>
   </si>
   <si>
     <t>STAC Services</t>
@@ -170,28 +182,16 @@
     <t>William Ferguson</t>
   </si>
   <si>
-    <t>DNU-MicroLearn-In Cab Distractions</t>
-  </si>
-  <si>
     <t>DNU-NEW-MicroLearn Distracted Driving</t>
   </si>
   <si>
     <t>DNU-UpdatedNEWMicro-LearnSpeed</t>
   </si>
   <si>
-    <t>Alert Driving</t>
-  </si>
-  <si>
-    <t>Micro-Learn Safe Following Distance</t>
-  </si>
-  <si>
     <t>Alejandro Garza</t>
   </si>
   <si>
     <t>Michael Vesely</t>
-  </si>
-  <si>
-    <t>Speed Management</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -614,16 +614,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>1227</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -643,16 +643,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>1229</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -672,16 +672,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>1228</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -701,16 +701,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>1230</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -730,16 +730,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>1232</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -759,16 +759,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>1231</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -788,16 +788,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>1233</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -817,16 +817,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>1234</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -846,16 +846,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>1227</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -875,16 +875,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>1229</v>
       </c>
       <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -904,16 +904,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>1228</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>14</v>
@@ -937,21 +937,21 @@
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>1230</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>12</v>
@@ -975,21 +975,21 @@
       <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>1232</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1009,16 +1009,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>1231</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1038,16 +1038,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>1233</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>12</v>
@@ -1071,21 +1071,21 @@
       <c r="J19" s="2"/>
       <c r="K19" s="1"/>
       <c r="M19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>1234</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>1229</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>1228</v>
       </c>
       <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>14</v>
@@ -1167,21 +1167,21 @@
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="M23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>1230</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>14</v>
@@ -1205,21 +1205,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>1232</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1239,16 +1239,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27">
         <v>1231</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1268,16 +1268,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>1233</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1297,16 +1297,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>1234</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30">
         <v>1229</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>1228</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E32">
         <v>1230</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>1232</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>1231</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1471,16 +1471,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>1233</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1500,16 +1500,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E36">
         <v>1234</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -1529,16 +1529,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E37">
         <v>1229</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1558,16 +1558,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E38">
         <v>1228</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1587,16 +1587,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E39">
         <v>1230</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1616,16 +1616,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>1232</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1645,16 +1645,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E41">
         <v>1231</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E42">
         <v>1233</v>
       </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1703,16 +1703,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E43">
         <v>1234</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1732,16 +1732,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E44">
         <v>1229</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1761,16 +1761,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E45">
         <v>1228</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1790,16 +1790,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E46">
         <v>1230</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E47">
         <v>1232</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1848,16 +1848,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E48">
         <v>1231</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E49">
         <v>1233</v>
       </c>
       <c r="F49" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E50">
         <v>1234</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -1935,16 +1935,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E51">
         <v>1229</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -1964,16 +1964,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E52">
         <v>1228</v>
       </c>
       <c r="F52" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1993,16 +1993,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E53">
         <v>1230</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2022,16 +2022,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E54">
         <v>1232</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E55">
         <v>1231</v>
       </c>
       <c r="F55" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -2080,16 +2080,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E56">
         <v>1233</v>
       </c>
       <c r="F56" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2109,16 +2109,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E57">
         <v>1234</v>
       </c>
       <c r="F57" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2138,16 +2138,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E58">
         <v>1229</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2167,16 +2167,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E59">
         <v>1228</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E60">
         <v>1230</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>12</v>
@@ -2229,21 +2229,21 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E62">
         <v>1232</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E63">
         <v>1231</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E64">
         <v>1233</v>
       </c>
       <c r="F64" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E65">
         <v>1234</v>
       </c>
       <c r="F65" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E66">
         <v>1229</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E67">
         <v>1228</v>
       </c>
       <c r="F67" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2408,16 +2408,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E68">
         <v>1230</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2437,16 +2437,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E69">
         <v>1232</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E70">
         <v>1231</v>
       </c>
       <c r="F70" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E71">
         <v>1233</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>13</v>
@@ -2524,16 +2524,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E72">
         <v>1234</v>
       </c>
       <c r="F72" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2553,16 +2553,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E73">
         <v>1229</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E74">
         <v>1228</v>
       </c>
       <c r="F74" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E75">
         <v>1230</v>
       </c>
       <c r="F75" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2644,21 +2644,21 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E77">
         <v>1232</v>
       </c>
       <c r="F77" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2678,16 +2678,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E78">
         <v>1231</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2707,16 +2707,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E79">
         <v>1233</v>
       </c>
       <c r="F79" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2736,16 +2736,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E80">
         <v>1234</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2765,16 +2765,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E81">
         <v>1229</v>
       </c>
       <c r="F81" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E82">
         <v>1228</v>
       </c>
       <c r="F82" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2823,16 +2823,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E83">
         <v>1230</v>
       </c>
       <c r="F83" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2852,16 +2852,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E84">
         <v>1232</v>
       </c>
       <c r="F84" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2881,16 +2881,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E85">
         <v>1231</v>
       </c>
       <c r="F85" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2910,16 +2910,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>1234</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2939,16 +2939,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E87">
         <v>1229</v>
       </c>
       <c r="F87" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -2968,16 +2968,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E88">
         <v>1228</v>
       </c>
       <c r="F88" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -2997,16 +2997,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E89">
         <v>1230</v>
       </c>
       <c r="F89" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3026,16 +3026,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E90">
         <v>1232</v>
       </c>
       <c r="F90" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3055,16 +3055,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E91">
         <v>1231</v>
       </c>
       <c r="F91" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3084,16 +3084,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E92">
         <v>1234</v>
       </c>
       <c r="F92" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3113,16 +3113,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E93">
         <v>1229</v>
       </c>
       <c r="F93" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3142,16 +3142,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E94">
         <v>1228</v>
       </c>
       <c r="F94" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3171,16 +3171,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E95">
         <v>1230</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>12</v>
@@ -3204,21 +3204,21 @@
       <c r="J96" s="2"/>
       <c r="K96" s="1"/>
       <c r="M96" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E97">
         <v>1232</v>
       </c>
       <c r="F97" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3238,16 +3238,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E98">
         <v>1231</v>
       </c>
       <c r="F98" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3267,16 +3267,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E99">
         <v>1234</v>
       </c>
       <c r="F99" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3296,16 +3296,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E100">
         <v>1229</v>
       </c>
       <c r="F100" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3325,16 +3325,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E101">
         <v>1228</v>
       </c>
       <c r="F101" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>12</v>
@@ -3358,21 +3358,21 @@
       <c r="J102" s="2"/>
       <c r="K102" s="1"/>
       <c r="M102" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E103">
         <v>1230</v>
       </c>
       <c r="F103" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E104">
         <v>1232</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3421,16 +3421,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E105">
         <v>1231</v>
       </c>
       <c r="F105" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3450,16 +3450,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E106">
         <v>1234</v>
       </c>
       <c r="F106" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3479,16 +3479,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E107">
         <v>1229</v>
       </c>
       <c r="F107" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3508,16 +3508,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E108">
         <v>1228</v>
       </c>
       <c r="F108" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3537,16 +3537,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E109">
         <v>1230</v>
       </c>
       <c r="F109" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3566,16 +3566,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E110">
         <v>1232</v>
       </c>
       <c r="F110" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3595,16 +3595,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E111">
         <v>1231</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3624,16 +3624,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E112">
         <v>1234</v>
       </c>
       <c r="F112" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3653,16 +3653,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E113">
         <v>1229</v>
       </c>
       <c r="F113" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E114">
         <v>1228</v>
       </c>
       <c r="F114" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3711,16 +3711,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E115">
         <v>1230</v>
       </c>
       <c r="F115" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3740,16 +3740,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E116">
         <v>1232</v>
       </c>
       <c r="F116" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3769,16 +3769,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E117">
         <v>1231</v>
       </c>
       <c r="F117" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3798,16 +3798,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E118">
         <v>1234</v>
       </c>
       <c r="F118" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3827,16 +3827,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E119">
         <v>1229</v>
       </c>
       <c r="F119" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3856,16 +3856,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E120">
         <v>1228</v>
       </c>
       <c r="F120" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3885,16 +3885,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E121">
         <v>1230</v>
       </c>
       <c r="F121" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E122">
         <v>1232</v>
       </c>
       <c r="F122" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3943,16 +3943,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E123">
         <v>1231</v>
       </c>
       <c r="F123" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E124">
         <v>1234</v>
       </c>
       <c r="F124" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -4001,16 +4001,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E125">
         <v>1229</v>
       </c>
       <c r="F125" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4030,16 +4030,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E126">
         <v>1230</v>
       </c>
       <c r="F126" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E127">
         <v>1232</v>
       </c>
       <c r="F127" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4088,16 +4088,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E128">
         <v>1231</v>
       </c>
       <c r="F128" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4117,16 +4117,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E129">
         <v>1229</v>
       </c>
       <c r="F129" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4146,16 +4146,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E130">
         <v>1230</v>
       </c>
       <c r="F130" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4175,16 +4175,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E131">
         <v>1232</v>
       </c>
       <c r="F131" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4204,16 +4204,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E132">
         <v>1231</v>
       </c>
       <c r="F132" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4233,16 +4233,16 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E133">
         <v>1229</v>
       </c>
       <c r="F133" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4262,16 +4262,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E134">
         <v>1230</v>
       </c>
       <c r="F134" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4291,16 +4291,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E135">
         <v>1232</v>
       </c>
       <c r="F135" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4320,16 +4320,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E136">
         <v>1231</v>
       </c>
       <c r="F136" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4349,16 +4349,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E137">
         <v>5138</v>
       </c>
       <c r="F137" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4378,16 +4378,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E138">
         <v>1229</v>
       </c>
       <c r="F138" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4407,16 +4407,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E139">
         <v>1230</v>
       </c>
       <c r="F139" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4436,16 +4436,16 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E140">
         <v>1232</v>
       </c>
       <c r="F140" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4465,16 +4465,16 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E141">
         <v>1231</v>
       </c>
       <c r="F141" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4494,16 +4494,16 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E142">
         <v>5138</v>
       </c>
       <c r="F142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4523,16 +4523,16 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E143">
         <v>1229</v>
       </c>
       <c r="F143" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4552,16 +4552,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E144">
         <v>1230</v>
       </c>
       <c r="F144" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4581,16 +4581,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E145">
         <v>1232</v>
       </c>
       <c r="F145" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4610,16 +4610,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E146">
         <v>1231</v>
       </c>
       <c r="F146" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4639,16 +4639,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E147">
         <v>1229</v>
       </c>
       <c r="F147" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E148">
         <v>1230</v>
       </c>
       <c r="F148" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4697,16 +4697,16 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E149">
         <v>1232</v>
       </c>
       <c r="F149" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4726,16 +4726,16 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E150">
         <v>1231</v>
       </c>
       <c r="F150" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -4755,16 +4755,16 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E151">
         <v>1229</v>
       </c>
       <c r="F151" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4784,16 +4784,16 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E152">
         <v>1230</v>
       </c>
       <c r="F152" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4813,16 +4813,16 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E153">
         <v>1232</v>
       </c>
       <c r="F153" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -4842,16 +4842,16 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E154">
         <v>1231</v>
       </c>
       <c r="F154" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4871,16 +4871,16 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E155">
         <v>1229</v>
       </c>
       <c r="F155" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4900,16 +4900,16 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E156">
         <v>1230</v>
       </c>
       <c r="F156" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4929,16 +4929,16 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E157">
         <v>5544</v>
       </c>
       <c r="F157" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4958,16 +4958,16 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E158">
         <v>1232</v>
       </c>
       <c r="F158" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -4987,16 +4987,16 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E159">
         <v>1231</v>
       </c>
       <c r="F159" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5016,16 +5016,16 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E160">
         <v>5544</v>
       </c>
       <c r="F160" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5045,16 +5045,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E161">
         <v>1229</v>
       </c>
       <c r="F161" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5074,16 +5074,16 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E162">
         <v>1230</v>
       </c>
       <c r="F162" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -5103,16 +5103,16 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E163">
         <v>1232</v>
       </c>
       <c r="F163" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>13</v>
@@ -5132,16 +5132,16 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E164">
         <v>1231</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5161,16 +5161,16 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E165">
         <v>1229</v>
       </c>
       <c r="F165" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5190,16 +5190,16 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E166">
         <v>1230</v>
       </c>
       <c r="F166" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5219,16 +5219,16 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E167">
         <v>5544</v>
       </c>
       <c r="F167" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5248,16 +5248,16 @@
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E168">
         <v>1232</v>
       </c>
       <c r="F168" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5277,16 +5277,16 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E169">
         <v>1231</v>
       </c>
       <c r="F169" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -12457,6 +12457,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -15780,6 +15781,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -15790,14 +15792,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -15823,6 +15828,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -15832,9 +15838,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -42772,6 +42780,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -42779,6 +42788,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -42786,6 +42796,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -42801,6 +42812,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -42810,6 +42822,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -42817,9 +42830,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -42827,12 +42846,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -42840,12 +42862,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -42857,9 +42882,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -42874,6 +42901,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -42900,6 +42928,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -42910,7 +42939,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -42918,6 +42952,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -42929,6 +42964,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -42936,6 +42972,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -42950,13 +42987,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -42967,15 +43010,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -42991,6 +43037,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -43009,6 +43056,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -43020,6 +43068,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -43037,18 +43086,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -43077,6 +43131,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -43084,9 +43139,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -43109,12 +43166,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -43129,9 +43189,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -43147,12 +43209,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -43173,6 +43237,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -43184,9 +43249,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -43198,6 +43265,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -43237,9 +43305,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -43247,9 +43317,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -43260,6 +43332,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -43267,18 +43340,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -43286,6 +43367,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -43296,6 +43378,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -43322,15 +43405,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -43352,6 +43439,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -43359,9 +43447,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -43369,6 +43459,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -43380,6 +43471,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -43394,6 +43486,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -43403,6 +43499,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -43414,6 +43511,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -43424,10 +43522,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -43435,6 +43538,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -43449,6 +43553,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -43471,6 +43576,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -43490,25 +43596,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -43516,6 +43634,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -43523,15 +43642,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -43545,6 +43671,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -43563,9 +43690,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -43573,9 +43702,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -43583,6 +43714,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -43599,10 +43731,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94CF86E2-E895-44E7-B4AE-28E2451AD80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A47FC4A-0DB6-4EFA-8C90-665463D905D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -134,16 +134,19 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
-    <t>3 points of contact</t>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
     <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
@@ -565,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -580,47 +583,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>1227</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -641,15 +644,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>1229</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -670,15 +673,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>1228</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -699,15 +702,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>1230</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -728,15 +731,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>1232</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -757,15 +760,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>1231</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -786,15 +789,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>1233</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -815,15 +818,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>1234</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -844,18 +847,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>1227</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -873,18 +876,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>1229</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -902,18 +905,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>1228</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -931,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -939,18 +942,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>1230</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -968,7 +971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2"/>
@@ -976,18 +979,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1232</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
         <v>10</v>
@@ -1007,16 +1010,16 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1231</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1036,16 +1039,16 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>1233</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -1073,16 +1076,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>1234</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1102,16 +1105,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>1229</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1131,16 +1134,16 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>1228</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1168,16 +1171,16 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>1230</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1205,16 +1208,16 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>1232</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1234,16 +1237,16 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>1231</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1263,16 +1266,16 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>1233</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -1292,16 +1295,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>1234</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -1321,16 +1324,16 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>1229</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -1350,16 +1353,16 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>1228</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1379,16 +1382,16 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>1230</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1408,16 +1411,16 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>1232</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
         <v>10</v>
@@ -1437,16 +1440,16 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>1231</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G34" t="s">
         <v>10</v>
@@ -1466,16 +1469,16 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35">
         <v>1233</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1495,16 +1498,16 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <v>1234</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -1524,16 +1527,16 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>1229</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -1553,16 +1556,16 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <v>1228</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1582,16 +1585,16 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <v>1230</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1611,16 +1614,16 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <v>1232</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
@@ -1640,16 +1643,16 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>1231</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G41" t="s">
         <v>10</v>
@@ -1669,16 +1672,16 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42">
         <v>1233</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -1698,16 +1701,16 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>1234</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1727,13 +1730,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>1229</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -1756,13 +1759,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>1228</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -1785,13 +1788,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>1230</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
@@ -1814,13 +1817,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C47">
         <v>1232</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -1843,13 +1846,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>1231</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -1872,13 +1875,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C49">
         <v>1233</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F49" t="s">
         <v>21</v>
@@ -1901,13 +1904,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>1234</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F50" t="s">
         <v>21</v>
@@ -1930,13 +1933,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51">
         <v>1229</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F51" t="s">
         <v>18</v>
@@ -1959,13 +1962,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C52">
         <v>1228</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -1988,13 +1991,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C53">
         <v>1230</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -2017,13 +2020,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C54">
         <v>1232</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" t="s">
         <v>18</v>
@@ -2046,13 +2049,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55">
         <v>1231</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -2075,13 +2078,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C56">
         <v>1233</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>
@@ -2104,13 +2107,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C57">
         <v>1234</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -2133,13 +2136,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C58">
         <v>1229</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -2162,13 +2165,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C59">
         <v>1228</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -2191,13 +2194,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C60">
         <v>1230</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -2228,13 +2231,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C62">
         <v>1232</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
         <v>19</v>
@@ -2257,13 +2260,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C63">
         <v>1231</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
         <v>19</v>
@@ -2286,13 +2289,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C64">
         <v>1233</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64" t="s">
         <v>19</v>
@@ -2315,13 +2318,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C65">
         <v>1234</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F65" t="s">
         <v>19</v>
@@ -2344,16 +2347,16 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C66">
         <v>1229</v>
       </c>
       <c r="D66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G66" t="s">
         <v>13</v>
@@ -2373,16 +2376,16 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C67">
         <v>1228</v>
       </c>
       <c r="D67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2402,16 +2405,16 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C68">
         <v>1230</v>
       </c>
       <c r="D68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -2431,16 +2434,16 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C69">
         <v>1232</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2460,16 +2463,16 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C70">
         <v>1231</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
@@ -2489,16 +2492,16 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C71">
         <v>1233</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G71" t="s">
         <v>13</v>
@@ -2518,16 +2521,16 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C72">
         <v>1234</v>
       </c>
       <c r="D72" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2547,16 +2550,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C73">
         <v>1229</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -2576,16 +2579,16 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C74">
         <v>1228</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2605,16 +2608,16 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C75">
         <v>1230</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -2642,16 +2645,16 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C77">
         <v>1232</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2671,16 +2674,16 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C78">
         <v>1231</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2700,16 +2703,16 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C79">
         <v>1233</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G79" t="s">
         <v>13</v>
@@ -2729,16 +2732,16 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C80">
         <v>1234</v>
       </c>
       <c r="D80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G80" t="s">
         <v>13</v>
@@ -2758,13 +2761,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C81">
         <v>1229</v>
       </c>
       <c r="D81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
@@ -2787,13 +2790,13 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C82">
         <v>1228</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F82" t="s">
         <v>23</v>
@@ -2816,13 +2819,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C83">
         <v>1230</v>
       </c>
       <c r="D83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -2845,13 +2848,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C84">
         <v>1232</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -2874,13 +2877,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C85">
         <v>1231</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -2903,13 +2906,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C86">
         <v>1234</v>
       </c>
       <c r="D86" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
@@ -2932,13 +2935,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C87">
         <v>1229</v>
       </c>
       <c r="D87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F87" t="s">
         <v>33</v>
@@ -2961,13 +2964,13 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C88">
         <v>1228</v>
       </c>
       <c r="D88" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F88" t="s">
         <v>33</v>
@@ -2990,13 +2993,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C89">
         <v>1230</v>
       </c>
       <c r="D89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" t="s">
         <v>33</v>
@@ -3019,13 +3022,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90">
         <v>1232</v>
       </c>
       <c r="D90" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F90" t="s">
         <v>33</v>
@@ -3048,13 +3051,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C91">
         <v>1231</v>
       </c>
       <c r="D91" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F91" t="s">
         <v>33</v>
@@ -3077,13 +3080,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C92">
         <v>1234</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F92" t="s">
         <v>33</v>
@@ -3106,13 +3109,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C93">
         <v>1229</v>
       </c>
       <c r="D93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F93" t="s">
         <v>22</v>
@@ -3135,13 +3138,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C94">
         <v>1228</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
@@ -3164,13 +3167,13 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C95">
         <v>1230</v>
       </c>
       <c r="D95" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F95" t="s">
         <v>22</v>
@@ -3201,13 +3204,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C97">
         <v>1232</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F97" t="s">
         <v>22</v>
@@ -3230,13 +3233,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C98">
         <v>1231</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F98" t="s">
         <v>22</v>
@@ -3259,13 +3262,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C99">
         <v>1234</v>
       </c>
       <c r="D99" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F99" t="s">
         <v>22</v>
@@ -3288,13 +3291,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C100">
         <v>1229</v>
       </c>
       <c r="D100" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F100" t="s">
         <v>34</v>
@@ -3317,13 +3320,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C101">
         <v>1228</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F101" t="s">
         <v>34</v>
@@ -3354,13 +3357,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C103">
         <v>1230</v>
       </c>
       <c r="D103" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -3383,13 +3386,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C104">
         <v>1232</v>
       </c>
       <c r="D104" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F104" t="s">
         <v>34</v>
@@ -3412,13 +3415,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C105">
         <v>1231</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F105" t="s">
         <v>34</v>
@@ -3441,13 +3444,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>1234</v>
       </c>
       <c r="D106" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F106" t="s">
         <v>34</v>
@@ -3470,13 +3473,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C107">
         <v>1229</v>
       </c>
       <c r="D107" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F107" t="s">
         <v>17</v>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C108">
         <v>1228</v>
       </c>
       <c r="D108" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F108" t="s">
         <v>17</v>
@@ -3528,13 +3531,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C109">
         <v>1230</v>
       </c>
       <c r="D109" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F109" t="s">
         <v>17</v>
@@ -3557,13 +3560,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C110">
         <v>1232</v>
       </c>
       <c r="D110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F110" t="s">
         <v>17</v>
@@ -3586,13 +3589,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C111">
         <v>1231</v>
       </c>
       <c r="D111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F111" t="s">
         <v>17</v>
@@ -3615,13 +3618,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C112">
         <v>1234</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F112" t="s">
         <v>17</v>
@@ -3644,16 +3647,16 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C113">
         <v>1229</v>
       </c>
       <c r="D113" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F113" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G113" t="s">
         <v>13</v>
@@ -3673,16 +3676,16 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C114">
         <v>1228</v>
       </c>
       <c r="D114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G114" t="s">
         <v>13</v>
@@ -3702,16 +3705,16 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C115">
         <v>1230</v>
       </c>
       <c r="D115" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F115" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G115" t="s">
         <v>13</v>
@@ -3731,16 +3734,16 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C116">
         <v>1232</v>
       </c>
       <c r="D116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F116" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G116" t="s">
         <v>10</v>
@@ -3760,16 +3763,16 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C117">
         <v>1231</v>
       </c>
       <c r="D117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F117" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G117" t="s">
         <v>13</v>
@@ -3789,16 +3792,16 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C118">
         <v>1234</v>
       </c>
       <c r="D118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F118" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G118" t="s">
         <v>13</v>
@@ -3818,13 +3821,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119">
         <v>1229</v>
       </c>
       <c r="D119" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F119" t="s">
         <v>25</v>
@@ -3847,13 +3850,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C120">
         <v>1228</v>
       </c>
       <c r="D120" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F120" t="s">
         <v>25</v>
@@ -3876,13 +3879,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C121">
         <v>1230</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F121" t="s">
         <v>25</v>
@@ -3905,13 +3908,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C122">
         <v>1232</v>
       </c>
       <c r="D122" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F122" t="s">
         <v>25</v>
@@ -3934,13 +3937,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C123">
         <v>1231</v>
       </c>
       <c r="D123" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F123" t="s">
         <v>25</v>
@@ -3963,13 +3966,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C124">
         <v>1234</v>
       </c>
       <c r="D124" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F124" t="s">
         <v>25</v>
@@ -3992,13 +3995,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C125">
         <v>1229</v>
       </c>
       <c r="D125" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -4021,13 +4024,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C126">
         <v>1230</v>
       </c>
       <c r="D126" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -4050,13 +4053,13 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C127">
         <v>1232</v>
       </c>
       <c r="D127" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -4079,13 +4082,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C128">
         <v>1231</v>
       </c>
       <c r="D128" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -4108,13 +4111,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C129">
         <v>1229</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F129" t="s">
         <v>18</v>
@@ -4137,13 +4140,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C130">
         <v>1230</v>
       </c>
       <c r="D130" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F130" t="s">
         <v>18</v>
@@ -4166,13 +4169,13 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C131">
         <v>1232</v>
       </c>
       <c r="D131" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F131" t="s">
         <v>18</v>
@@ -4195,13 +4198,13 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C132">
         <v>1231</v>
       </c>
       <c r="D132" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F132" t="s">
         <v>18</v>
@@ -4224,13 +4227,13 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C133">
         <v>1229</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F133" t="s">
         <v>19</v>
@@ -4253,13 +4256,13 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C134">
         <v>1230</v>
       </c>
       <c r="D134" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F134" t="s">
         <v>19</v>
@@ -4282,13 +4285,13 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C135">
         <v>1232</v>
       </c>
       <c r="D135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F135" t="s">
         <v>19</v>
@@ -4311,13 +4314,13 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C136">
         <v>1231</v>
       </c>
       <c r="D136" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F136" t="s">
         <v>19</v>
@@ -4340,13 +4343,13 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C137">
         <v>5138</v>
       </c>
       <c r="D137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F137" t="s">
         <v>26</v>
@@ -4369,13 +4372,13 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C138">
         <v>1229</v>
       </c>
       <c r="D138" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F138" t="s">
         <v>26</v>
@@ -4398,13 +4401,13 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C139">
         <v>1230</v>
       </c>
       <c r="D139" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F139" t="s">
         <v>26</v>
@@ -4427,13 +4430,13 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C140">
         <v>1232</v>
       </c>
       <c r="D140" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F140" t="s">
         <v>26</v>
@@ -4456,13 +4459,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C141">
         <v>1231</v>
       </c>
       <c r="D141" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F141" t="s">
         <v>26</v>
@@ -4485,13 +4488,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C142">
         <v>5138</v>
       </c>
       <c r="D142" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F142" t="s">
         <v>27</v>
@@ -4514,13 +4517,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C143">
         <v>1229</v>
       </c>
       <c r="D143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F143" t="s">
         <v>27</v>
@@ -4543,13 +4546,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C144">
         <v>1230</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F144" t="s">
         <v>27</v>
@@ -4572,13 +4575,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C145">
         <v>1232</v>
       </c>
       <c r="D145" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F145" t="s">
         <v>27</v>
@@ -4601,13 +4604,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C146">
         <v>1231</v>
       </c>
       <c r="D146" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F146" t="s">
         <v>27</v>
@@ -4630,13 +4633,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C147">
         <v>1229</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -4659,13 +4662,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C148">
         <v>1230</v>
       </c>
       <c r="D148" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -4688,13 +4691,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C149">
         <v>1232</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -4717,13 +4720,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C150">
         <v>1231</v>
       </c>
       <c r="D150" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -4746,13 +4749,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C151">
         <v>1229</v>
       </c>
       <c r="D151" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F151" t="s">
         <v>29</v>
@@ -4775,13 +4778,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C152">
         <v>1230</v>
       </c>
       <c r="D152" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F152" t="s">
         <v>29</v>
@@ -4804,13 +4807,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C153">
         <v>1232</v>
       </c>
       <c r="D153" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F153" t="s">
         <v>29</v>
@@ -4833,13 +4836,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C154">
         <v>1231</v>
       </c>
       <c r="D154" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
         <v>29</v>
@@ -4862,13 +4865,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C155">
         <v>1229</v>
       </c>
       <c r="D155" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F155" t="s">
         <v>20</v>
@@ -4891,13 +4894,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C156">
         <v>1230</v>
       </c>
       <c r="D156" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F156" t="s">
         <v>20</v>
@@ -4920,13 +4923,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C157">
         <v>5544</v>
       </c>
       <c r="D157" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F157" t="s">
         <v>20</v>
@@ -4949,13 +4952,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C158">
         <v>1232</v>
       </c>
       <c r="D158" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F158" t="s">
         <v>20</v>
@@ -4978,13 +4981,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C159">
         <v>1231</v>
       </c>
       <c r="D159" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F159" t="s">
         <v>20</v>
@@ -5007,13 +5010,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C160">
         <v>5544</v>
       </c>
       <c r="D160" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F160" t="s">
         <v>24</v>
@@ -5036,13 +5039,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C161">
         <v>1229</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F161" t="s">
         <v>30</v>
@@ -5065,13 +5068,13 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C162">
         <v>1230</v>
       </c>
       <c r="D162" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F162" t="s">
         <v>30</v>
@@ -5094,13 +5097,13 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C163">
         <v>1232</v>
       </c>
       <c r="D163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F163" t="s">
         <v>30</v>
@@ -5123,13 +5126,13 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C164">
         <v>1231</v>
       </c>
       <c r="D164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F164" t="s">
         <v>30</v>
@@ -5152,13 +5155,13 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C165">
         <v>1229</v>
       </c>
       <c r="D165" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F165" t="s">
         <v>22</v>
@@ -5181,13 +5184,13 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C166">
         <v>1230</v>
       </c>
       <c r="D166" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F166" t="s">
         <v>22</v>
@@ -5210,13 +5213,13 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C167">
         <v>5544</v>
       </c>
       <c r="D167" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F167" t="s">
         <v>22</v>
@@ -5239,13 +5242,13 @@
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C168">
         <v>1232</v>
       </c>
       <c r="D168" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F168" t="s">
         <v>22</v>
@@ -5268,13 +5271,13 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C169">
         <v>1231</v>
       </c>
       <c r="D169" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F169" t="s">
         <v>22</v>
@@ -5296,40 +5299,157 @@
       </c>
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H170" s="2"/>
-      <c r="I170" s="1"/>
-      <c r="J170" s="2"/>
-      <c r="K170" s="1"/>
+      <c r="B170" t="s">
+        <v>39</v>
+      </c>
+      <c r="C170">
+        <v>1229</v>
+      </c>
+      <c r="D170" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170" t="s">
+        <v>31</v>
+      </c>
+      <c r="G170" t="s">
+        <v>13</v>
+      </c>
+      <c r="H170" s="2">
+        <v>0</v>
+      </c>
+      <c r="I170" s="1">
+        <v>46237.854513888888</v>
+      </c>
+      <c r="J170" s="2">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H171" s="2"/>
-      <c r="I171" s="1"/>
-      <c r="J171" s="2"/>
-      <c r="K171" s="1"/>
+      <c r="B171" t="s">
+        <v>39</v>
+      </c>
+      <c r="C171">
+        <v>1230</v>
+      </c>
+      <c r="D171" t="s">
+        <v>43</v>
+      </c>
+      <c r="F171" t="s">
+        <v>31</v>
+      </c>
+      <c r="G171" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="2">
+        <v>0</v>
+      </c>
+      <c r="I171" s="1">
+        <v>46237.854513888888</v>
+      </c>
+      <c r="J171" s="2">
+        <v>0</v>
+      </c>
+      <c r="K171" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H172" s="2"/>
-      <c r="I172" s="1"/>
-      <c r="J172" s="2"/>
-      <c r="K172" s="1"/>
+      <c r="B172" t="s">
+        <v>39</v>
+      </c>
+      <c r="C172">
+        <v>5544</v>
+      </c>
+      <c r="D172" t="s">
+        <v>51</v>
+      </c>
+      <c r="F172" t="s">
+        <v>31</v>
+      </c>
+      <c r="G172" t="s">
+        <v>12</v>
+      </c>
+      <c r="H172" s="2">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="I172" s="1">
+        <v>46237.855208333334</v>
+      </c>
+      <c r="J172" s="2">
+        <v>0</v>
+      </c>
+      <c r="K172" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H173" s="2"/>
       <c r="I173" s="1"/>
       <c r="J173" s="2"/>
-      <c r="K173" s="1"/>
+      <c r="K173" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H174" s="2"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="2"/>
-      <c r="K174" s="1"/>
+      <c r="B174" t="s">
+        <v>39</v>
+      </c>
+      <c r="C174">
+        <v>1232</v>
+      </c>
+      <c r="D174" t="s">
+        <v>44</v>
+      </c>
+      <c r="F174" t="s">
+        <v>31</v>
+      </c>
+      <c r="G174" t="s">
+        <v>13</v>
+      </c>
+      <c r="H174" s="2">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>46237.855902777781</v>
+      </c>
+      <c r="J174" s="2">
+        <v>0</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H175" s="2"/>
-      <c r="I175" s="1"/>
-      <c r="J175" s="2"/>
-      <c r="K175" s="1"/>
+      <c r="B175" t="s">
+        <v>39</v>
+      </c>
+      <c r="C175">
+        <v>1231</v>
+      </c>
+      <c r="D175" t="s">
+        <v>45</v>
+      </c>
+      <c r="F175" t="s">
+        <v>31</v>
+      </c>
+      <c r="G175" t="s">
+        <v>13</v>
+      </c>
+      <c r="H175" s="2">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>46237.855902777781</v>
+      </c>
+      <c r="J175" s="2">
+        <v>0</v>
+      </c>
+      <c r="K175" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H176" s="2"/>
@@ -15915,9 +16035,11 @@
       <c r="K1944" s="1"/>
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
       <c r="K1946" s="1"/>
     </row>
@@ -15983,6 +16105,7 @@
       <c r="K1958" s="1"/>
     </row>
     <row r="1959" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1959" s="2"/>
       <c r="I1959" s="1"/>
       <c r="K1959" s="1"/>
     </row>
@@ -16025,6 +16148,7 @@
       <c r="K1966" s="1"/>
     </row>
     <row r="1967" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:11" x14ac:dyDescent="0.25">
@@ -16038,6 +16162,7 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
       <c r="K1970" s="1"/>
     </row>
@@ -16108,6 +16233,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -16137,6 +16263,7 @@
       <c r="K1988" s="1"/>
     </row>
     <row r="1989" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
       <c r="K1989" s="1"/>
     </row>
@@ -16158,6 +16285,7 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -16236,6 +16364,7 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -46417,6 +46546,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -46431,11 +46561,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46446,10 +46578,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -46467,14 +46602,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46485,14 +46623,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -46519,6 +46660,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -46527,6 +46669,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -46539,22 +46682,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46573,6 +46721,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46583,10 +46732,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -46595,10 +46746,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -46612,82 +46765,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -46701,6 +46869,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46711,6 +46880,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -46718,6 +46888,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -46726,86 +46897,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46822,26 +47006,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -46872,6 +47062,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -46881,10 +47072,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -46897,14 +47090,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -46913,14 +47109,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -46939,26 +47138,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46977,6 +47182,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -46985,10 +47191,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -46997,6 +47205,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -47009,10 +47218,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -47021,6 +47232,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -47029,14 +47241,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -47045,14 +47260,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -47069,76 +47287,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -47152,31 +47379,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -47189,10 +47423,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -47201,10 +47437,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -47213,6 +47451,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47227,10 +47466,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -47239,10 +47480,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -47256,6 +47499,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47271,14 +47515,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47296,14 +47543,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -47316,10 +47566,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -47328,14 +47580,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -47344,10 +47599,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -47356,14 +47613,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -47385,6 +47645,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -47393,39 +47654,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A47FC4A-0DB6-4EFA-8C90-665463D905D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB67A23D-E9D6-4FD6-84F0-EE9D5077FD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="52">
   <si>
     <t>Company Name</t>
   </si>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>39</v>
       </c>
@@ -818,7 +818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -1206,7 +1206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>39</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>39</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>39</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>39</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>39</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>39</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>39</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>39</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>39</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>39</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>46237.854513888888</v>
       </c>
       <c r="J170" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K170" s="1" t="s">
         <v>11</v>
@@ -5350,7 +5350,7 @@
         <v>46237.854513888888</v>
       </c>
       <c r="J171" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K171" s="1" t="s">
         <v>11</v>
@@ -5370,38 +5370,59 @@
         <v>31</v>
       </c>
       <c r="G172" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H172" s="2">
-        <v>9.2592592592592588E-5</v>
+        <v>7.7777777777777776E-3</v>
       </c>
       <c r="I172" s="1">
         <v>46237.855208333334</v>
       </c>
       <c r="J172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H173" s="2"/>
-      <c r="I173" s="1"/>
-      <c r="J173" s="2"/>
+      <c r="B173" t="s">
+        <v>39</v>
+      </c>
+      <c r="C173">
+        <v>1232</v>
+      </c>
+      <c r="D173" t="s">
+        <v>44</v>
+      </c>
+      <c r="F173" t="s">
+        <v>31</v>
+      </c>
+      <c r="G173" t="s">
+        <v>10</v>
+      </c>
+      <c r="H173" s="2">
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="I173" s="1">
+        <v>46237.855902777781</v>
+      </c>
+      <c r="J173" s="2">
+        <v>3</v>
+      </c>
       <c r="K173" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>39</v>
       </c>
       <c r="C174">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D174" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F174" t="s">
         <v>31</v>
@@ -5416,40 +5437,17 @@
         <v>46237.855902777781</v>
       </c>
       <c r="J174" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B175" t="s">
-        <v>39</v>
-      </c>
-      <c r="C175">
-        <v>1231</v>
-      </c>
-      <c r="D175" t="s">
-        <v>45</v>
-      </c>
-      <c r="F175" t="s">
-        <v>31</v>
-      </c>
-      <c r="G175" t="s">
-        <v>13</v>
-      </c>
-      <c r="H175" s="2">
-        <v>0</v>
-      </c>
-      <c r="I175" s="1">
-        <v>46237.855902777781</v>
-      </c>
-      <c r="J175" s="2">
-        <v>0</v>
-      </c>
-      <c r="K175" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H175" s="2"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="2"/>
+      <c r="K175" s="1"/>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H176" s="2"/>
@@ -5469,7 +5467,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5529,7 +5527,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5637,7 +5635,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5829,7 +5827,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -6345,7 +6343,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6411,7 +6409,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6423,7 +6421,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6519,7 +6517,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6531,7 +6529,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6627,7 +6625,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6687,7 +6685,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -16101,6 +16099,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -16138,6 +16137,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -16202,6 +16202,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -16233,11 +16234,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -16248,6 +16249,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -16323,6 +16325,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -16333,6 +16336,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -16364,7 +16368,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -45657,6 +45660,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45949,6 +45953,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46259,6 +46265,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46383,6 +46390,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46394,6 +46402,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46542,6 +46551,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -46552,10 +46562,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -46589,15 +46601,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -46638,18 +46653,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46665,6 +46684,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -46674,10 +46694,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -46713,10 +46735,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -46742,6 +46766,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -46756,6 +46781,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46790,6 +46816,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -46799,6 +46826,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -46808,6 +46836,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -46822,15 +46851,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -46860,6 +46890,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46880,11 +46911,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -46893,6 +46926,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -46922,6 +46956,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -46931,10 +46966,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -46949,14 +46986,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -46976,10 +47016,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -46999,9 +47041,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -47036,18 +47081,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -47062,12 +47111,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -47082,10 +47131,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -47105,6 +47156,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -47124,6 +47176,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -47133,6 +47186,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -47178,6 +47232,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -47187,6 +47242,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -47201,6 +47257,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -47210,10 +47267,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -47228,6 +47287,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -47237,6 +47297,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -47256,6 +47317,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -47275,10 +47337,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47288,6 +47352,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -47298,10 +47363,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -47316,18 +47383,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -47347,10 +47418,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -47370,6 +47443,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47400,7 +47474,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -47415,10 +47488,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -47433,6 +47508,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -47447,11 +47523,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47461,6 +47537,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -47476,6 +47553,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -47490,6 +47568,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47510,6 +47589,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -47535,11 +47615,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -47558,15 +47640,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -47576,6 +47659,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -47595,6 +47679,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -47609,6 +47694,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -47628,10 +47714,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47641,6 +47729,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -47651,6 +47740,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -47687,7 +47777,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -47696,6 +47785,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -47709,10 +47799,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\STAC-Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB67A23D-E9D6-4FD6-84F0-EE9D5077FD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19E3B1A2-E764-4DE3-8723-E3C852F48230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -143,19 +143,19 @@
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
+  </si>
+  <si>
+    <t>DNU-MicroLearn-In Cab Distractions</t>
+  </si>
+  <si>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>3 points of contact</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
-  </si>
-  <si>
-    <t>DNU-Fatigue</t>
-  </si>
-  <si>
-    <t>DNU-MicroLearn-In Cab Distractions</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>STAC Services</t>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>39</v>
       </c>
@@ -818,7 +818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -858,7 +858,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -887,7 +887,7 @@
         <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -916,7 +916,7 @@
         <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -953,7 +953,7 @@
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -990,7 +990,7 @@
         <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1048,7 +1048,7 @@
         <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -1085,7 +1085,7 @@
         <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1114,7 +1114,7 @@
         <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1143,7 +1143,7 @@
         <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1180,7 +1180,7 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1206,7 +1206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>39</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1246,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -1304,7 +1304,7 @@
         <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>39</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>39</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>39</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>41</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>39</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>42</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2617,7 +2617,7 @@
         <v>43</v>
       </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -2654,7 +2654,7 @@
         <v>44</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2683,7 +2683,7 @@
         <v>45</v>
       </c>
       <c r="F78" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2712,7 +2712,7 @@
         <v>46</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G79" t="s">
         <v>13</v>
@@ -2741,7 +2741,7 @@
         <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G80" t="s">
         <v>13</v>
@@ -2788,7 +2788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>39</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>39</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>41</v>
       </c>
       <c r="F100" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G100" t="s">
         <v>13</v>
@@ -3329,7 +3329,7 @@
         <v>42</v>
       </c>
       <c r="F101" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G101" t="s">
         <v>12</v>
@@ -3366,7 +3366,7 @@
         <v>43</v>
       </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G103" t="s">
         <v>13</v>
@@ -3395,7 +3395,7 @@
         <v>44</v>
       </c>
       <c r="F104" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G104" t="s">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>45</v>
       </c>
       <c r="F105" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G105" t="s">
         <v>10</v>
@@ -3453,7 +3453,7 @@
         <v>47</v>
       </c>
       <c r="F106" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G106" t="s">
         <v>13</v>
@@ -3616,7 +3616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>39</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>39</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>39</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>39</v>
       </c>
@@ -5467,7 +5467,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5527,7 +5527,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5635,7 +5635,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5827,7 +5827,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -6343,7 +6343,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6409,7 +6409,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6421,7 +6421,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6517,7 +6517,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6529,7 +6529,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6625,7 +6625,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6685,7 +6685,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -16086,6 +16086,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -16095,6 +16096,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -16234,6 +16236,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -16287,7 +16290,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -45660,7 +45662,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45953,8 +45954,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46265,7 +46264,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46390,7 +46388,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46402,7 +46399,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46551,35 +46547,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46590,44 +46580,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46638,37 +46619,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46679,52 +46653,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46735,17 +46699,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46756,32 +46717,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46791,106 +46746,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46900,7 +46835,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46911,127 +46845,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -47041,62 +46949,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -47116,67 +47011,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -47186,38 +47068,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -47232,117 +47107,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47351,99 +47203,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47453,23 +47286,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -47478,52 +47307,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -47537,38 +47356,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47578,7 +47390,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47589,23 +47400,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47615,37 +47422,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -47654,72 +47454,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47729,76 +47515,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
